--- a/Shortfundly_Internship_Candidates_Dummy.xlsx
+++ b/Shortfundly_Internship_Candidates_Dummy.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X137"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -5160,9 +5160,5411 @@
         <v>27/10/2026, 4:45:29 pm</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SF-MEET-1793102019657-782</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C65" t="str">
+        <v>candidate.1793102019657-0.3044845964148515@shortfundly.com</v>
+      </c>
+      <c r="D65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I65" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J65" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K65" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O65" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S65" t="str">
+        <v>None</v>
+      </c>
+      <c r="T65" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U65" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V65" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W65" t="str">
+        <v>No</v>
+      </c>
+      <c r="X65" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SF-MEET-1793102020160-449</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C66" t="str">
+        <v>candidate.1793102020160-0.9073141648207913@shortfundly.com</v>
+      </c>
+      <c r="D66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I66" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J66" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K66" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O66" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S66" t="str">
+        <v>None</v>
+      </c>
+      <c r="T66" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U66" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V66" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W66" t="str">
+        <v>No</v>
+      </c>
+      <c r="X66" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SF-MEET-1793102020214-759</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C67" t="str">
+        <v>candidate.1793102020214-0.9992992682180777@shortfundly.com</v>
+      </c>
+      <c r="D67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I67" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J67" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K67" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N67" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O67" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S67" t="str">
+        <v>None</v>
+      </c>
+      <c r="T67" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U67" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V67" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W67" t="str">
+        <v>No</v>
+      </c>
+      <c r="X67" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SF-MEET-1793102020270-455</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C68" t="str">
+        <v>candidate.1793102020270-0.7629132312238296@shortfundly.com</v>
+      </c>
+      <c r="D68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H68" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I68" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J68" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K68" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O68" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S68" t="str">
+        <v>None</v>
+      </c>
+      <c r="T68" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U68" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V68" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W68" t="str">
+        <v>No</v>
+      </c>
+      <c r="X68" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SF-MEET-1793102020380-24</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C69" t="str">
+        <v>candidate.1793102020380-0.6530412174979834@shortfundly.com</v>
+      </c>
+      <c r="D69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I69" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J69" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K69" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O69" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S69" t="str">
+        <v>None</v>
+      </c>
+      <c r="T69" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U69" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V69" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W69" t="str">
+        <v>No</v>
+      </c>
+      <c r="X69" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SF-MEET-1793102020642-164</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C70" t="str">
+        <v>candidate.1793102020642-0.10108115867753842@shortfundly.com</v>
+      </c>
+      <c r="D70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I70" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J70" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K70" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N70" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O70" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S70" t="str">
+        <v>None</v>
+      </c>
+      <c r="T70" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U70" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V70" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W70" t="str">
+        <v>No</v>
+      </c>
+      <c r="X70" t="str">
+        <v>27/10/2026, 5:23:40 pm</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SF-MEET-1793102020859-84</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C71" t="str">
+        <v>candidate.1793102020859-0.28108505082572643@shortfundly.com</v>
+      </c>
+      <c r="D71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I71" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J71" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K71" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N71" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O71" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S71" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T71" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U71" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V71" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W71" t="str">
+        <v>No</v>
+      </c>
+      <c r="X71" t="str">
+        <v>27/10/2026, 5:23:41 pm</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SF-MEET-1793102021542-332</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C72" t="str">
+        <v>candidate.1793102021542-0.6030494710343742@shortfundly.com</v>
+      </c>
+      <c r="D72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I72" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J72" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K72" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N72" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O72" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S72" t="str">
+        <v>None</v>
+      </c>
+      <c r="T72" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U72" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V72" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W72" t="str">
+        <v>No</v>
+      </c>
+      <c r="X72" t="str">
+        <v>27/10/2026, 5:23:41 pm</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>SF-MEET-1793102021816-625</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C73" t="str">
+        <v>candidate.1793102021816-0.24992700573416904@shortfundly.com</v>
+      </c>
+      <c r="D73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I73" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J73" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K73" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N73" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O73" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S73" t="str">
+        <v>None</v>
+      </c>
+      <c r="T73" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U73" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V73" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W73" t="str">
+        <v>No</v>
+      </c>
+      <c r="X73" t="str">
+        <v>27/10/2026, 5:23:41 pm</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>SF-MEET-1793105528289-997</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C74" t="str">
+        <v>candidate.1793105528289-0.42732968048803766@shortfundly.com</v>
+      </c>
+      <c r="D74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I74" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J74" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K74" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N74" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O74" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S74" t="str">
+        <v>None</v>
+      </c>
+      <c r="T74" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U74" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V74" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W74" t="str">
+        <v>No</v>
+      </c>
+      <c r="X74" t="str">
+        <v>27/10/2026, 6:22:08 pm</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>SF-MEET-1793105528979-280</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C75" t="str">
+        <v>candidate.1793105528979-0.5346623022122032@shortfundly.com</v>
+      </c>
+      <c r="D75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I75" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J75" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K75" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O75" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S75" t="str">
+        <v>None</v>
+      </c>
+      <c r="T75" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U75" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V75" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W75" t="str">
+        <v>No</v>
+      </c>
+      <c r="X75" t="str">
+        <v>27/10/2026, 6:22:08 pm</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>SF-MEET-1793105529043-861</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C76" t="str">
+        <v>candidate.1793105529043-0.46373333172121933@shortfundly.com</v>
+      </c>
+      <c r="D76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I76" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J76" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K76" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N76" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O76" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S76" t="str">
+        <v>None</v>
+      </c>
+      <c r="T76" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U76" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V76" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W76" t="str">
+        <v>No</v>
+      </c>
+      <c r="X76" t="str">
+        <v>27/10/2026, 6:22:09 pm</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SF-MEET-1793105529106-358</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C77" t="str">
+        <v>candidate.1793105529106-0.6922633794823984@shortfundly.com</v>
+      </c>
+      <c r="D77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I77" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J77" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K77" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O77" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S77" t="str">
+        <v>None</v>
+      </c>
+      <c r="T77" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U77" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V77" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W77" t="str">
+        <v>No</v>
+      </c>
+      <c r="X77" t="str">
+        <v>27/10/2026, 6:22:09 pm</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SF-MEET-1793105529231-641</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C78" t="str">
+        <v>candidate.1793105529231-0.7215628485964798@shortfundly.com</v>
+      </c>
+      <c r="D78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I78" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J78" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K78" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N78" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O78" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S78" t="str">
+        <v>None</v>
+      </c>
+      <c r="T78" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U78" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V78" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W78" t="str">
+        <v>No</v>
+      </c>
+      <c r="X78" t="str">
+        <v>27/10/2026, 6:22:09 pm</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SF-MEET-1793105529541-12</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C79" t="str">
+        <v>candidate.1793105529541-0.7622789805294689@shortfundly.com</v>
+      </c>
+      <c r="D79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I79" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J79" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K79" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N79" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O79" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S79" t="str">
+        <v>None</v>
+      </c>
+      <c r="T79" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U79" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V79" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W79" t="str">
+        <v>No</v>
+      </c>
+      <c r="X79" t="str">
+        <v>27/10/2026, 6:22:09 pm</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>SF-MEET-1793105529797-277</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C80" t="str">
+        <v>candidate.1793105529797-0.2032675862782417@shortfundly.com</v>
+      </c>
+      <c r="D80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I80" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J80" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K80" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O80" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S80" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T80" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U80" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V80" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W80" t="str">
+        <v>No</v>
+      </c>
+      <c r="X80" t="str">
+        <v>27/10/2026, 6:22:10 pm</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>SF-MEET-1793105530595-310</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C81" t="str">
+        <v>candidate.1793105530595-0.8453933092132907@shortfundly.com</v>
+      </c>
+      <c r="D81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I81" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J81" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K81" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N81" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O81" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S81" t="str">
+        <v>None</v>
+      </c>
+      <c r="T81" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U81" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V81" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W81" t="str">
+        <v>No</v>
+      </c>
+      <c r="X81" t="str">
+        <v>27/10/2026, 6:22:10 pm</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>SF-MEET-1793105530891-90</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C82" t="str">
+        <v>candidate.1793105530891-0.6216205261930233@shortfundly.com</v>
+      </c>
+      <c r="D82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I82" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J82" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K82" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N82" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O82" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S82" t="str">
+        <v>None</v>
+      </c>
+      <c r="T82" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U82" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V82" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W82" t="str">
+        <v>No</v>
+      </c>
+      <c r="X82" t="str">
+        <v>27/10/2026, 6:22:10 pm</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>SF-MEET-1793112802765-985</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C83" t="str">
+        <v>candidate.1793112802765-0.16413644510486436@shortfundly.com</v>
+      </c>
+      <c r="D83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I83" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J83" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K83" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N83" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O83" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S83" t="str">
+        <v>None</v>
+      </c>
+      <c r="T83" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U83" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V83" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W83" t="str">
+        <v>No</v>
+      </c>
+      <c r="X83" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>SF-MEET-1793112803268-159</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C84" t="str">
+        <v>candidate.1793112803268-0.25959793128063857@shortfundly.com</v>
+      </c>
+      <c r="D84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I84" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J84" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K84" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O84" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S84" t="str">
+        <v>None</v>
+      </c>
+      <c r="T84" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U84" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V84" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W84" t="str">
+        <v>No</v>
+      </c>
+      <c r="X84" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>SF-MEET-1793112803323-901</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C85" t="str">
+        <v>candidate.1793112803323-0.40619811569192465@shortfundly.com</v>
+      </c>
+      <c r="D85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I85" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J85" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K85" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N85" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O85" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S85" t="str">
+        <v>None</v>
+      </c>
+      <c r="T85" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U85" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V85" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W85" t="str">
+        <v>No</v>
+      </c>
+      <c r="X85" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>SF-MEET-1793112803378-273</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C86" t="str">
+        <v>candidate.1793112803378-0.09155169785368333@shortfundly.com</v>
+      </c>
+      <c r="D86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I86" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J86" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K86" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N86" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O86" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S86" t="str">
+        <v>None</v>
+      </c>
+      <c r="T86" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U86" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V86" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W86" t="str">
+        <v>No</v>
+      </c>
+      <c r="X86" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>SF-MEET-1793112803493-525</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C87" t="str">
+        <v>candidate.1793112803493-0.16588509649968763@shortfundly.com</v>
+      </c>
+      <c r="D87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I87" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J87" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K87" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N87" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O87" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S87" t="str">
+        <v>None</v>
+      </c>
+      <c r="T87" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U87" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V87" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W87" t="str">
+        <v>No</v>
+      </c>
+      <c r="X87" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>SF-MEET-1793112803786-820</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C88" t="str">
+        <v>candidate.1793112803786-0.17692722309266895@shortfundly.com</v>
+      </c>
+      <c r="D88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I88" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J88" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K88" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N88" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O88" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S88" t="str">
+        <v>None</v>
+      </c>
+      <c r="T88" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U88" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V88" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W88" t="str">
+        <v>No</v>
+      </c>
+      <c r="X88" t="str">
+        <v>27/10/2026, 8:23:23 pm</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>SF-MEET-1793112804023-575</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C89" t="str">
+        <v>candidate.1793112804023-0.8335317830458101@shortfundly.com</v>
+      </c>
+      <c r="D89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I89" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J89" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K89" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N89" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O89" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S89" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T89" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U89" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V89" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W89" t="str">
+        <v>No</v>
+      </c>
+      <c r="X89" t="str">
+        <v>27/10/2026, 8:23:24 pm</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>SF-MEET-1793112804701-869</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C90" t="str">
+        <v>candidate.1793112804701-0.5745463922674117@shortfundly.com</v>
+      </c>
+      <c r="D90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I90" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J90" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K90" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N90" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O90" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S90" t="str">
+        <v>None</v>
+      </c>
+      <c r="T90" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U90" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V90" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W90" t="str">
+        <v>No</v>
+      </c>
+      <c r="X90" t="str">
+        <v>27/10/2026, 8:23:24 pm</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>SF-MEET-1793112804970-99</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C91" t="str">
+        <v>candidate.1793112804970-0.7093386619628448@shortfundly.com</v>
+      </c>
+      <c r="D91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I91" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J91" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K91" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N91" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O91" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S91" t="str">
+        <v>None</v>
+      </c>
+      <c r="T91" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U91" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V91" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W91" t="str">
+        <v>No</v>
+      </c>
+      <c r="X91" t="str">
+        <v>27/10/2026, 8:23:25 pm</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>SF-MEET-1793112846647-848</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C92" t="str">
+        <v>candidate.1793112846647-0.49132965417304264@shortfundly.com</v>
+      </c>
+      <c r="D92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I92" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J92" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K92" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N92" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O92" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S92" t="str">
+        <v>None</v>
+      </c>
+      <c r="T92" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U92" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V92" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W92" t="str">
+        <v>No</v>
+      </c>
+      <c r="X92" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>SF-MEET-1793112847166-150</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C93" t="str">
+        <v>candidate.1793112847166-0.6814036426839167@shortfundly.com</v>
+      </c>
+      <c r="D93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I93" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J93" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K93" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N93" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O93" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S93" t="str">
+        <v>None</v>
+      </c>
+      <c r="T93" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U93" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V93" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W93" t="str">
+        <v>No</v>
+      </c>
+      <c r="X93" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>SF-MEET-1793112847221-850</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C94" t="str">
+        <v>candidate.1793112847221-0.7158596220337251@shortfundly.com</v>
+      </c>
+      <c r="D94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I94" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J94" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K94" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N94" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O94" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S94" t="str">
+        <v>None</v>
+      </c>
+      <c r="T94" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U94" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V94" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W94" t="str">
+        <v>No</v>
+      </c>
+      <c r="X94" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>SF-MEET-1793112847273-373</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C95" t="str">
+        <v>candidate.1793112847273-0.1207784230344725@shortfundly.com</v>
+      </c>
+      <c r="D95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I95" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J95" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K95" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N95" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O95" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S95" t="str">
+        <v>None</v>
+      </c>
+      <c r="T95" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U95" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V95" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W95" t="str">
+        <v>No</v>
+      </c>
+      <c r="X95" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>SF-MEET-1793112847386-666</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C96" t="str">
+        <v>candidate.1793112847386-0.8232501485096952@shortfundly.com</v>
+      </c>
+      <c r="D96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I96" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J96" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K96" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N96" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O96" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S96" t="str">
+        <v>None</v>
+      </c>
+      <c r="T96" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U96" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V96" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W96" t="str">
+        <v>No</v>
+      </c>
+      <c r="X96" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>SF-MEET-1793112847649-244</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C97" t="str">
+        <v>candidate.1793112847649-0.14768034302124644@shortfundly.com</v>
+      </c>
+      <c r="D97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I97" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J97" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K97" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N97" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O97" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S97" t="str">
+        <v>None</v>
+      </c>
+      <c r="T97" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U97" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V97" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W97" t="str">
+        <v>No</v>
+      </c>
+      <c r="X97" t="str">
+        <v>27/10/2026, 8:24:07 pm</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>SF-MEET-1793112847867-334</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C98" t="str">
+        <v>candidate.1793112847867-0.935934657220278@shortfundly.com</v>
+      </c>
+      <c r="D98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I98" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J98" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K98" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N98" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O98" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S98" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T98" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U98" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V98" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W98" t="str">
+        <v>No</v>
+      </c>
+      <c r="X98" t="str">
+        <v>27/10/2026, 8:24:08 pm</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>SF-MEET-1793112848539-180</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C99" t="str">
+        <v>candidate.1793112848539-0.6019932721606396@shortfundly.com</v>
+      </c>
+      <c r="D99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I99" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J99" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K99" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N99" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O99" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S99" t="str">
+        <v>None</v>
+      </c>
+      <c r="T99" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U99" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V99" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W99" t="str">
+        <v>No</v>
+      </c>
+      <c r="X99" t="str">
+        <v>27/10/2026, 8:24:08 pm</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>SF-MEET-1793112848796-252</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C100" t="str">
+        <v>candidate.1793112848796-0.8598835694585689@shortfundly.com</v>
+      </c>
+      <c r="D100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I100" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J100" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K100" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M100" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N100" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O100" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S100" t="str">
+        <v>None</v>
+      </c>
+      <c r="T100" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U100" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V100" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W100" t="str">
+        <v>No</v>
+      </c>
+      <c r="X100" t="str">
+        <v>27/10/2026, 8:24:08 pm</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>SF-MEET-1793112897911-867</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C101" t="str">
+        <v>candidate.1793112897911-0.5575888293698169@shortfundly.com</v>
+      </c>
+      <c r="D101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I101" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J101" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K101" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M101" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N101" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O101" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S101" t="str">
+        <v>None</v>
+      </c>
+      <c r="T101" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U101" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V101" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W101" t="str">
+        <v>No</v>
+      </c>
+      <c r="X101" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>SF-MEET-1793112898449-784</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C102" t="str">
+        <v>candidate.1793112898449-0.5795967536990233@shortfundly.com</v>
+      </c>
+      <c r="D102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I102" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J102" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K102" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M102" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N102" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O102" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S102" t="str">
+        <v>None</v>
+      </c>
+      <c r="T102" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U102" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V102" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W102" t="str">
+        <v>No</v>
+      </c>
+      <c r="X102" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>SF-MEET-1793112898505-853</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C103" t="str">
+        <v>candidate.1793112898505-0.07123367309881268@shortfundly.com</v>
+      </c>
+      <c r="D103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I103" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J103" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K103" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N103" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O103" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S103" t="str">
+        <v>None</v>
+      </c>
+      <c r="T103" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U103" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V103" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W103" t="str">
+        <v>No</v>
+      </c>
+      <c r="X103" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>SF-MEET-1793112898563-891</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C104" t="str">
+        <v>candidate.1793112898563-0.4855312723417886@shortfundly.com</v>
+      </c>
+      <c r="D104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I104" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J104" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K104" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L104" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M104" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N104" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O104" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="R104" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S104" t="str">
+        <v>None</v>
+      </c>
+      <c r="T104" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U104" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V104" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W104" t="str">
+        <v>No</v>
+      </c>
+      <c r="X104" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>SF-MEET-1793112898678-398</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C105" t="str">
+        <v>candidate.1793112898678-0.7302112089549762@shortfundly.com</v>
+      </c>
+      <c r="D105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I105" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J105" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K105" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M105" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O105" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S105" t="str">
+        <v>None</v>
+      </c>
+      <c r="T105" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U105" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V105" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W105" t="str">
+        <v>No</v>
+      </c>
+      <c r="X105" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>SF-MEET-1793112898942-995</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C106" t="str">
+        <v>candidate.1793112898943-0.9592461162934943@shortfundly.com</v>
+      </c>
+      <c r="D106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I106" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J106" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K106" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M106" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N106" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O106" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+      <c r="R106" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S106" t="str">
+        <v>None</v>
+      </c>
+      <c r="T106" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U106" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V106" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W106" t="str">
+        <v>No</v>
+      </c>
+      <c r="X106" t="str">
+        <v>27/10/2026, 8:24:58 pm</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>SF-MEET-1793112899149-891</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C107" t="str">
+        <v>candidate.1793112899149-0.371394715235575@shortfundly.com</v>
+      </c>
+      <c r="D107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I107" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J107" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K107" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M107" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N107" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O107" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+      <c r="R107" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S107" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T107" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U107" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V107" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W107" t="str">
+        <v>No</v>
+      </c>
+      <c r="X107" t="str">
+        <v>27/10/2026, 8:24:59 pm</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>SF-MEET-1793112899811-321</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C108" t="str">
+        <v>candidate.1793112899811-0.31749758917185356@shortfundly.com</v>
+      </c>
+      <c r="D108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I108" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J108" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K108" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N108" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O108" t="str">
+        <v>Leaved Internship</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S108" t="str">
+        <v>None</v>
+      </c>
+      <c r="T108" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U108" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V108" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W108" t="str">
+        <v>No</v>
+      </c>
+      <c r="X108" t="str">
+        <v>27/10/2026, 10:11:15 pm</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>SF-MEET-1793112900075-512</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C109" t="str">
+        <v>candidate.1793112900075-0.9552991685784759@shortfundly.com</v>
+      </c>
+      <c r="D109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I109" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J109" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K109" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M109" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N109" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O109" t="str">
+        <v>Leaved Internship</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S109" t="str">
+        <v>None</v>
+      </c>
+      <c r="T109" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U109" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V109" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W109" t="str">
+        <v>No</v>
+      </c>
+      <c r="X109" t="str">
+        <v>27/10/2026, 10:11:07 pm</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>SF-INT-2026-3877</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Dharshana</v>
+      </c>
+      <c r="C110" t="str">
+        <v>dachudharshana17@gmail.com</v>
+      </c>
+      <c r="D110" t="str">
+        <v>9698202557</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Rathinam Global University</v>
+      </c>
+      <c r="H110" t="str">
+        <v xml:space="preserve">BSc IT </v>
+      </c>
+      <c r="I110" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="J110" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="K110" t="str">
+        <v>3 Months</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M110" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N110" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O110" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S110" t="str">
+        <v>None</v>
+      </c>
+      <c r="T110" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U110" t="str">
+        <v>Priyanka Nair</v>
+      </c>
+      <c r="V110" t="str">
+        <v>Rahul Kapoor</v>
+      </c>
+      <c r="W110" t="str">
+        <v>No</v>
+      </c>
+      <c r="X110" t="str">
+        <v>27/10/2026, 9:43:57 pm</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>SF-MEET-1793120380172-419</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C111" t="str">
+        <v>candidate.1793120380172-0.4293313236518328@shortfundly.com</v>
+      </c>
+      <c r="D111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I111" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J111" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K111" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M111" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N111" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O111" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S111" t="str">
+        <v>None</v>
+      </c>
+      <c r="T111" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U111" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V111" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W111" t="str">
+        <v>No</v>
+      </c>
+      <c r="X111" t="str">
+        <v>27/10/2026, 10:29:40 pm</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>SF-MEET-1793120380818-155</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C112" t="str">
+        <v>candidate.1793120380818-0.7543950245453167@shortfundly.com</v>
+      </c>
+      <c r="D112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I112" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J112" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K112" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L112" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M112" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N112" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O112" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S112" t="str">
+        <v>None</v>
+      </c>
+      <c r="T112" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U112" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V112" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W112" t="str">
+        <v>No</v>
+      </c>
+      <c r="X112" t="str">
+        <v>27/10/2026, 10:29:40 pm</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>SF-MEET-1793120380889-77</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C113" t="str">
+        <v>candidate.1793120380889-0.7601102666632251@shortfundly.com</v>
+      </c>
+      <c r="D113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I113" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J113" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K113" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L113" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M113" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N113" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O113" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S113" t="str">
+        <v>None</v>
+      </c>
+      <c r="T113" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U113" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V113" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W113" t="str">
+        <v>No</v>
+      </c>
+      <c r="X113" t="str">
+        <v>27/10/2026, 10:29:40 pm</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>SF-MEET-1793120380957-116</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C114" t="str">
+        <v>candidate.1793120380957-0.12194510153688976@shortfundly.com</v>
+      </c>
+      <c r="D114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I114" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J114" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K114" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L114" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M114" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N114" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O114" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S114" t="str">
+        <v>None</v>
+      </c>
+      <c r="T114" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U114" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V114" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W114" t="str">
+        <v>No</v>
+      </c>
+      <c r="X114" t="str">
+        <v>27/10/2026, 10:29:40 pm</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>SF-MEET-1793120381079-596</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C115" t="str">
+        <v>candidate.1793120381079-0.20859757291847503@shortfundly.com</v>
+      </c>
+      <c r="D115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I115" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J115" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K115" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L115" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M115" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N115" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O115" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S115" t="str">
+        <v>None</v>
+      </c>
+      <c r="T115" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U115" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V115" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W115" t="str">
+        <v>No</v>
+      </c>
+      <c r="X115" t="str">
+        <v>27/10/2026, 10:29:41 pm</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>SF-MEET-1793120381435-105</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C116" t="str">
+        <v>candidate.1793120381435-0.7852527467068291@shortfundly.com</v>
+      </c>
+      <c r="D116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H116" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I116" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J116" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K116" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L116" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M116" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N116" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O116" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>0</v>
+      </c>
+      <c r="R116" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S116" t="str">
+        <v>None</v>
+      </c>
+      <c r="T116" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U116" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V116" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W116" t="str">
+        <v>No</v>
+      </c>
+      <c r="X116" t="str">
+        <v>27/10/2026, 10:29:41 pm</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>SF-MEET-1793120381721-320</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C117" t="str">
+        <v>candidate.1793120381721-0.1366325490461383@shortfundly.com</v>
+      </c>
+      <c r="D117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H117" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I117" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J117" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K117" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L117" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M117" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N117" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O117" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>0</v>
+      </c>
+      <c r="R117" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S117" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T117" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U117" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V117" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W117" t="str">
+        <v>No</v>
+      </c>
+      <c r="X117" t="str">
+        <v>27/10/2026, 10:29:42 pm</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>SF-MEET-1793120382615-932</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C118" t="str">
+        <v>candidate.1793120382615-0.6458301512693833@shortfundly.com</v>
+      </c>
+      <c r="D118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I118" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J118" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K118" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L118" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M118" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N118" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O118" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S118" t="str">
+        <v>None</v>
+      </c>
+      <c r="T118" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U118" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V118" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W118" t="str">
+        <v>No</v>
+      </c>
+      <c r="X118" t="str">
+        <v>27/10/2026, 10:29:42 pm</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>SF-MEET-1793120382931-286</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C119" t="str">
+        <v>candidate.1793120382931-0.08177873332343022@shortfundly.com</v>
+      </c>
+      <c r="D119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H119" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I119" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J119" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K119" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L119" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M119" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N119" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O119" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S119" t="str">
+        <v>None</v>
+      </c>
+      <c r="T119" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U119" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V119" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W119" t="str">
+        <v>No</v>
+      </c>
+      <c r="X119" t="str">
+        <v>27/10/2026, 10:29:43 pm</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>SF-MEET-1793120429286-519</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C120" t="str">
+        <v>candidate.1793120429286-0.6700569862445196@shortfundly.com</v>
+      </c>
+      <c r="D120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H120" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I120" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J120" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K120" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L120" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M120" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N120" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O120" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S120" t="str">
+        <v>None</v>
+      </c>
+      <c r="T120" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U120" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V120" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W120" t="str">
+        <v>No</v>
+      </c>
+      <c r="X120" t="str">
+        <v>27/10/2026, 10:30:30 pm</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>SF-MEET-1793120430540-66</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C121" t="str">
+        <v>candidate.1793120430540-0.7033184813327127@shortfundly.com</v>
+      </c>
+      <c r="D121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H121" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I121" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J121" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K121" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L121" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M121" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O121" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S121" t="str">
+        <v>None</v>
+      </c>
+      <c r="T121" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U121" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V121" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W121" t="str">
+        <v>No</v>
+      </c>
+      <c r="X121" t="str">
+        <v>27/10/2026, 10:30:30 pm</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>SF-MEET-1793120430591-893</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C122" t="str">
+        <v>candidate.1793120430591-0.888082707295493@shortfundly.com</v>
+      </c>
+      <c r="D122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H122" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I122" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J122" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K122" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L122" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M122" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N122" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O122" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S122" t="str">
+        <v>None</v>
+      </c>
+      <c r="T122" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U122" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V122" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W122" t="str">
+        <v>No</v>
+      </c>
+      <c r="X122" t="str">
+        <v>27/10/2026, 10:30:30 pm</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>SF-MEET-1793120430644-707</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C123" t="str">
+        <v>candidate.1793120430644-0.3832217529719081@shortfundly.com</v>
+      </c>
+      <c r="D123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H123" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I123" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J123" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K123" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L123" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M123" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N123" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O123" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S123" t="str">
+        <v>None</v>
+      </c>
+      <c r="T123" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U123" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V123" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W123" t="str">
+        <v>No</v>
+      </c>
+      <c r="X123" t="str">
+        <v>27/10/2026, 10:30:30 pm</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>SF-MEET-1793120430752-753</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C124" t="str">
+        <v>candidate.1793120430752-0.8173007856890152@shortfundly.com</v>
+      </c>
+      <c r="D124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H124" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I124" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J124" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K124" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L124" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M124" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N124" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O124" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S124" t="str">
+        <v>None</v>
+      </c>
+      <c r="T124" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U124" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V124" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W124" t="str">
+        <v>No</v>
+      </c>
+      <c r="X124" t="str">
+        <v>27/10/2026, 10:30:30 pm</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>SF-MEET-1793120431019-442</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C125" t="str">
+        <v>candidate.1793120431019-0.20052217077376377@shortfundly.com</v>
+      </c>
+      <c r="D125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I125" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J125" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K125" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L125" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M125" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N125" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O125" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S125" t="str">
+        <v>None</v>
+      </c>
+      <c r="T125" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U125" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V125" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W125" t="str">
+        <v>No</v>
+      </c>
+      <c r="X125" t="str">
+        <v>27/10/2026, 10:30:31 pm</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>SF-MEET-1793120431219-90</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C126" t="str">
+        <v>candidate.1793120431219-0.0929790432773705@shortfundly.com</v>
+      </c>
+      <c r="D126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I126" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J126" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K126" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L126" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M126" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N126" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O126" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S126" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T126" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U126" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V126" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W126" t="str">
+        <v>No</v>
+      </c>
+      <c r="X126" t="str">
+        <v>27/10/2026, 10:30:31 pm</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>SF-MEET-1793120431866-572</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C127" t="str">
+        <v>candidate.1793120431866-0.2926841592288474@shortfundly.com</v>
+      </c>
+      <c r="D127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I127" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J127" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K127" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L127" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M127" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N127" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O127" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S127" t="str">
+        <v>None</v>
+      </c>
+      <c r="T127" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U127" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V127" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W127" t="str">
+        <v>No</v>
+      </c>
+      <c r="X127" t="str">
+        <v>27/10/2026, 10:30:32 pm</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>SF-MEET-1793120432130-335</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C128" t="str">
+        <v>candidate.1793120432130-0.5929602478728448@shortfundly.com</v>
+      </c>
+      <c r="D128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I128" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J128" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K128" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L128" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M128" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N128" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O128" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S128" t="str">
+        <v>None</v>
+      </c>
+      <c r="T128" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U128" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V128" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W128" t="str">
+        <v>No</v>
+      </c>
+      <c r="X128" t="str">
+        <v>27/10/2026, 10:30:32 pm</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>SF-MEET-1793120480119-711</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C129" t="str">
+        <v>candidate.1793120480119-0.4384707146772082@shortfundly.com</v>
+      </c>
+      <c r="D129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I129" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J129" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K129" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L129" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M129" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N129" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O129" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S129" t="str">
+        <v>None</v>
+      </c>
+      <c r="T129" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U129" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V129" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W129" t="str">
+        <v>No</v>
+      </c>
+      <c r="X129" t="str">
+        <v>27/10/2026, 10:31:20 pm</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>SF-MEET-1793120480636-718</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C130" t="str">
+        <v>candidate.1793120480636-0.14058142314738908@shortfundly.com</v>
+      </c>
+      <c r="D130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I130" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J130" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K130" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L130" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M130" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N130" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O130" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S130" t="str">
+        <v>None</v>
+      </c>
+      <c r="T130" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U130" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V130" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W130" t="str">
+        <v>No</v>
+      </c>
+      <c r="X130" t="str">
+        <v>27/10/2026, 10:31:20 pm</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>SF-MEET-1793120480692-444</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C131" t="str">
+        <v>candidate.1793120480692-0.19837968092999525@shortfundly.com</v>
+      </c>
+      <c r="D131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I131" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J131" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K131" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L131" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M131" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N131" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O131" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S131" t="str">
+        <v>None</v>
+      </c>
+      <c r="T131" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U131" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V131" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W131" t="str">
+        <v>No</v>
+      </c>
+      <c r="X131" t="str">
+        <v>27/10/2026, 10:31:20 pm</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>SF-MEET-1793120480747-513</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C132" t="str">
+        <v>candidate.1793120480747-0.780509459474375@shortfundly.com</v>
+      </c>
+      <c r="D132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I132" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J132" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K132" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L132" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M132" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N132" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O132" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S132" t="str">
+        <v>None</v>
+      </c>
+      <c r="T132" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U132" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V132" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W132" t="str">
+        <v>No</v>
+      </c>
+      <c r="X132" t="str">
+        <v>27/10/2026, 10:31:20 pm</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>SF-MEET-1793120480856-608</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C133" t="str">
+        <v>candidate.1793120480856-0.8271473460036646@shortfundly.com</v>
+      </c>
+      <c r="D133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I133" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J133" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K133" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L133" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M133" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N133" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O133" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S133" t="str">
+        <v>None</v>
+      </c>
+      <c r="T133" t="str">
+        <v>https://meet.google.com/rec-over-lnk</v>
+      </c>
+      <c r="U133" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V133" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W133" t="str">
+        <v>No</v>
+      </c>
+      <c r="X133" t="str">
+        <v>27/10/2026, 10:31:20 pm</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>SF-MEET-1793120481120-217</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C134" t="str">
+        <v>candidate.1793120481120-0.34990886122755427@shortfundly.com</v>
+      </c>
+      <c r="D134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H134" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I134" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J134" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K134" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L134" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M134" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N134" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O134" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S134" t="str">
+        <v>None</v>
+      </c>
+      <c r="T134" t="str">
+        <v>https://meet.google.com/exi-stin-grm</v>
+      </c>
+      <c r="U134" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V134" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W134" t="str">
+        <v>No</v>
+      </c>
+      <c r="X134" t="str">
+        <v>27/10/2026, 10:31:21 pm</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>SF-MEET-1793120481335-970</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C135" t="str">
+        <v>candidate.1793120481335-0.8487344102606273@shortfundly.com</v>
+      </c>
+      <c r="D135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H135" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I135" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J135" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K135" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L135" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M135" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N135" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O135" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S135" t="str">
+        <v>Sprint 1 Tasks</v>
+      </c>
+      <c r="T135" t="str">
+        <v>https://meet.google.com/new-repl-aced</v>
+      </c>
+      <c r="U135" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V135" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W135" t="str">
+        <v>No</v>
+      </c>
+      <c r="X135" t="str">
+        <v>27/10/2026, 10:31:21 pm</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>SF-MEET-1793120482004-30</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C136" t="str">
+        <v>candidate.1793120482004-0.6813541284333348@shortfundly.com</v>
+      </c>
+      <c r="D136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H136" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I136" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J136" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K136" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L136" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M136" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N136" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O136" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S136" t="str">
+        <v>None</v>
+      </c>
+      <c r="T136" t="str">
+        <v>https://meet.google.com/con-curr-sync</v>
+      </c>
+      <c r="U136" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V136" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W136" t="str">
+        <v>No</v>
+      </c>
+      <c r="X136" t="str">
+        <v>27/10/2026, 10:31:22 pm</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>SF-MEET-1793120482280-721</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Meet Integration Candidate</v>
+      </c>
+      <c r="C137" t="str">
+        <v>candidate.1793120482280-0.18852559057385687@shortfundly.com</v>
+      </c>
+      <c r="D137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Web Developer Intern</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="G137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H137" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="I137" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J137" t="str">
+        <v>2026-12-01</v>
+      </c>
+      <c r="K137" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="L137" t="str">
+        <v>Online - Remote</v>
+      </c>
+      <c r="M137" t="str">
+        <v>Sent</v>
+      </c>
+      <c r="N137" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="O137" t="str">
+        <v>Not Assigned</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137" t="str">
+        <v>0%</v>
+      </c>
+      <c r="S137" t="str">
+        <v>None</v>
+      </c>
+      <c r="T137" t="str">
+        <v>Pending Assignment</v>
+      </c>
+      <c r="U137" t="str">
+        <v>M. Selvam</v>
+      </c>
+      <c r="V137" t="str">
+        <v>Tech Lead</v>
+      </c>
+      <c r="W137" t="str">
+        <v>No</v>
+      </c>
+      <c r="X137" t="str">
+        <v>27/10/2026, 10:31:22 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X137"/>
   </ignoredErrors>
 </worksheet>
 </file>